--- a/countries/is/2026-2029.xlsx
+++ b/countries/is/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>34</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>8.450795244687805</v>
       </c>
@@ -1171,9 +1168,6 @@
       <c r="O4" t="n">
         <v>135</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>33.55462817743688</v>
       </c>
@@ -1580,9 +1574,6 @@
       <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.4971056026286944</v>
       </c>
@@ -1992,9 +1983,6 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2404,9 +2392,6 @@
       <c r="P10" t="n">
         <v>22</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>5.468161628915639</v>
       </c>
@@ -2816,9 +2801,6 @@
       <c r="P12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -3218,9 +3200,6 @@
       <c r="P14" t="n">
         <v>7</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>1.73986960920043</v>
       </c>
@@ -3620,9 +3599,6 @@
       <c r="P16" t="n">
         <v>8</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>1.988422410514778</v>
       </c>
@@ -4032,9 +4008,6 @@
       <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4444,9 +4417,6 @@
       <c r="P20" t="n">
         <v>12</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>2.982633615772166</v>
       </c>
@@ -4856,9 +4826,6 @@
       <c r="P22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -5258,9 +5225,6 @@
       <c r="P24" t="n">
         <v>9</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>2.236975211829125</v>
       </c>
@@ -5660,9 +5624,6 @@
       <c r="P26" t="n">
         <v>19</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>4.722503224972597</v>
       </c>
@@ -6072,9 +6033,6 @@
       <c r="P28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6484,9 +6442,6 @@
       <c r="P30" t="n">
         <v>9</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>2.236975211829125</v>
       </c>
@@ -6896,9 +6851,6 @@
       <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -7298,9 +7250,6 @@
       <c r="P34" t="n">
         <v>21</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>5.219608827601292</v>
       </c>
@@ -7700,9 +7649,6 @@
       <c r="P36" t="n">
         <v>10</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>2.485528013143472</v>
       </c>
@@ -8112,9 +8058,6 @@
       <c r="P38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8524,9 +8467,6 @@
       <c r="P40" t="n">
         <v>11</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>2.734080814457819</v>
       </c>
@@ -8936,9 +8876,6 @@
       <c r="P42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -9338,9 +9275,6 @@
       <c r="P44" t="n">
         <v>30</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>7.456584039430417</v>
       </c>
@@ -9737,9 +9671,6 @@
       <c r="O46" t="n">
         <v>27</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>6.710925635487374</v>
       </c>
@@ -10143,9 +10074,6 @@
       <c r="O48" t="n">
         <v>123</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>30.57199456166471</v>
       </c>
@@ -10552,9 +10480,6 @@
       <c r="P50" t="n">
         <v>12</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>2.982633615772166</v>
       </c>
@@ -10964,9 +10889,6 @@
       <c r="P52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -11376,9 +11298,6 @@
       <c r="P54" t="n">
         <v>15</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>3.728292019715209</v>
       </c>
@@ -11788,9 +11707,6 @@
       <c r="P56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -12190,9 +12106,6 @@
       <c r="P58" t="n">
         <v>26</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>6.462372834173028</v>
       </c>
@@ -12592,9 +12505,6 @@
       <c r="P60" t="n">
         <v>7</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>1.73986960920043</v>
       </c>
@@ -13004,9 +12914,6 @@
       <c r="P62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -13416,9 +13323,6 @@
       <c r="P64" t="n">
         <v>11</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>2.734080814457819</v>
       </c>
@@ -13828,9 +13732,6 @@
       <c r="P66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -14230,9 +14131,6 @@
       <c r="P68" t="n">
         <v>19</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>4.722503224972597</v>
       </c>
@@ -14632,9 +14530,6 @@
       <c r="P70" t="n">
         <v>9</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>2.236975211829125</v>
       </c>
@@ -15044,9 +14939,6 @@
       <c r="P72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -15456,9 +15348,6 @@
       <c r="P74" t="n">
         <v>14</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>3.479739218400861</v>
       </c>
@@ -15868,9 +15757,6 @@
       <c r="P76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -16270,9 +16156,6 @@
       <c r="P78" t="n">
         <v>15</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>3.728292019715209</v>
       </c>
@@ -16672,9 +16555,6 @@
       <c r="P80" t="n">
         <v>4</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.9942112052573888</v>
       </c>
@@ -17084,9 +16964,6 @@
       <c r="P82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -17496,9 +17373,6 @@
       <c r="P84" t="n">
         <v>19</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>4.722503224972597</v>
       </c>
@@ -17908,9 +17782,6 @@
       <c r="P86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -18310,9 +18181,6 @@
       <c r="P88" t="n">
         <v>25</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>6.21382003285868</v>
       </c>
@@ -18709,9 +18577,6 @@
       <c r="O90" t="n">
         <v>30</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>7.456584039430417</v>
       </c>
@@ -19115,9 +18980,6 @@
       <c r="O92" t="n">
         <v>136</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>33.80318097875122</v>
       </c>
@@ -19524,9 +19386,6 @@
       <c r="P94" t="n">
         <v>5</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>1.242764006571736</v>
       </c>
@@ -19936,9 +19795,6 @@
       <c r="P96" t="n">
         <v>1</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -20348,9 +20204,6 @@
       <c r="P98" t="n">
         <v>7</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>1.73986960920043</v>
       </c>
@@ -20760,9 +20613,6 @@
       <c r="P100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -21162,9 +21012,6 @@
       <c r="P102" t="n">
         <v>13</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>3.231186417086514</v>
       </c>
@@ -21564,9 +21411,6 @@
       <c r="P104" t="n">
         <v>5</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>1.242764006571736</v>
       </c>
@@ -21976,9 +21820,6 @@
       <c r="P106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -22388,9 +22229,6 @@
       <c r="P108" t="n">
         <v>13</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>3.231186417086514</v>
       </c>
@@ -22800,9 +22638,6 @@
       <c r="P110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -23202,9 +23037,6 @@
       <c r="P112" t="n">
         <v>18</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>4.47395042365825</v>
       </c>
@@ -23604,9 +23436,6 @@
       <c r="P114" t="n">
         <v>4</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.9942112052573888</v>
       </c>
@@ -24016,9 +23845,6 @@
       <c r="P116" t="n">
         <v>1</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -24428,9 +24254,6 @@
       <c r="P118" t="n">
         <v>20</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>4.971056026286944</v>
       </c>
@@ -24840,9 +24663,6 @@
       <c r="P120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -25242,9 +25062,6 @@
       <c r="P122" t="n">
         <v>15</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>3.728292019715209</v>
       </c>
@@ -25644,9 +25461,6 @@
       <c r="P124" t="n">
         <v>5</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>1.242764006571736</v>
       </c>
@@ -26056,9 +25870,6 @@
       <c r="P126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -26468,9 +26279,6 @@
       <c r="P128" t="n">
         <v>11</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>2.734080814457819</v>
       </c>
@@ -26880,9 +26688,6 @@
       <c r="P130" t="n">
         <v>1</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -27282,9 +27087,6 @@
       <c r="P132" t="n">
         <v>14</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>3.479739218400861</v>
       </c>
@@ -27684,9 +27486,6 @@
       <c r="P134" t="n">
         <v>6</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>1.491316807886083</v>
       </c>
@@ -28096,9 +27895,6 @@
       <c r="P136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -28508,9 +28304,6 @@
       <c r="P138" t="n">
         <v>21</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>5.219608827601292</v>
       </c>
@@ -28920,9 +28713,6 @@
       <c r="P140" t="n">
         <v>3</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.7456584039430416</v>
       </c>
@@ -29322,9 +29112,6 @@
       <c r="P142" t="n">
         <v>7</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>1.73986960920043</v>
       </c>
@@ -29721,9 +29508,6 @@
       <c r="O144" t="n">
         <v>25</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>6.21382003285868</v>
       </c>
@@ -30127,9 +29911,6 @@
       <c r="O146" t="n">
         <v>97</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>24.10962172749168</v>
       </c>
@@ -30536,9 +30317,6 @@
       <c r="P148" t="n">
         <v>9</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>2.236975211829125</v>
       </c>
@@ -30948,9 +30726,6 @@
       <c r="P150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -31360,9 +31135,6 @@
       <c r="P152" t="n">
         <v>26</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>6.462372834173028</v>
       </c>
@@ -31772,9 +31544,6 @@
       <c r="P154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -32174,9 +31943,6 @@
       <c r="P156" t="n">
         <v>10</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>2.485528013143472</v>
       </c>
@@ -32576,9 +32342,6 @@
       <c r="P158" t="n">
         <v>3</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.7456584039430416</v>
       </c>
@@ -32988,9 +32751,6 @@
       <c r="P160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -33400,9 +33160,6 @@
       <c r="P162" t="n">
         <v>8</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>1.988422410514778</v>
       </c>
@@ -33812,9 +33569,6 @@
       <c r="P164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -34214,9 +33968,6 @@
       <c r="P166" t="n">
         <v>4</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.9942112052573888</v>
       </c>
@@ -34616,9 +34367,6 @@
       <c r="P168" t="n">
         <v>1</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -35028,9 +34776,6 @@
       <c r="P170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -35440,9 +35185,6 @@
       <c r="P172" t="n">
         <v>3</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.7456584039430416</v>
       </c>
@@ -35852,9 +35594,6 @@
       <c r="P174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -36254,9 +35993,6 @@
       <c r="P176" t="n">
         <v>9</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>2.236975211829125</v>
       </c>
@@ -36656,9 +36392,6 @@
       <c r="P178" t="n">
         <v>3</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.7456584039430416</v>
       </c>
@@ -37068,9 +36801,6 @@
       <c r="P180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -37480,9 +37210,6 @@
       <c r="P182" t="n">
         <v>2</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.4971056026286944</v>
       </c>
@@ -37892,9 +37619,6 @@
       <c r="P184" t="n">
         <v>1</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -38294,9 +38018,6 @@
       <c r="P186" t="n">
         <v>3</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.7456584039430416</v>
       </c>
@@ -38693,9 +38414,6 @@
       <c r="O188" t="n">
         <v>29</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>7.208031238116069</v>
       </c>
@@ -39099,9 +38817,6 @@
       <c r="O190" t="n">
         <v>125</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>31.0691001642934</v>
       </c>
@@ -39508,9 +39223,6 @@
       <c r="P192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -39920,9 +39632,6 @@
       <c r="P194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -40332,9 +40041,6 @@
       <c r="P196" t="n">
         <v>5</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>1.242764006571736</v>
       </c>
@@ -40744,9 +40450,6 @@
       <c r="P198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -41146,9 +40849,6 @@
       <c r="P200" t="n">
         <v>2</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.4971056026286944</v>
       </c>
@@ -41545,9 +41245,6 @@
       <c r="O202" t="n">
         <v>33</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>8.202242443373459</v>
       </c>
@@ -41950,9 +41647,6 @@
       </c>
       <c r="O204" t="n">
         <v>153</v>
-      </c>
-      <c r="Q204" t="n">
-        <v>0</v>
       </c>
       <c r="R204" t="n">
         <v>38.02857860109512</v>

--- a/countries/is/2026-2029.xlsx
+++ b/countries/is/2026-2029.xlsx
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         </is>
       </c>
       <c r="AT82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         </is>
       </c>
       <c r="AT90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         </is>
       </c>
       <c r="AT91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         </is>
       </c>
       <c r="AT92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         </is>
       </c>
       <c r="AT93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         </is>
       </c>
       <c r="AT96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         </is>
       </c>
       <c r="AT97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         </is>
       </c>
       <c r="AT116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         </is>
       </c>
       <c r="AT117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         </is>
       </c>
       <c r="AT126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         </is>
       </c>
       <c r="AT127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         </is>
       </c>
       <c r="AT136" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         </is>
       </c>
       <c r="AT144" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         </is>
       </c>
       <c r="AT145" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         </is>
       </c>
       <c r="AT146" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         </is>
       </c>
       <c r="AT147" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         </is>
       </c>
       <c r="AT150" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         </is>
       </c>
       <c r="AT160" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         </is>
       </c>
       <c r="AT161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         </is>
       </c>
       <c r="AT170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
@@ -35062,7 +35062,7 @@
         </is>
       </c>
       <c r="AT171" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         </is>
       </c>
       <c r="AT180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         </is>
       </c>
       <c r="AT181" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         </is>
       </c>
       <c r="AT188" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         </is>
       </c>
       <c r="AT189" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
@@ -38861,7 +38861,7 @@
         </is>
       </c>
       <c r="AT190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         </is>
       </c>
       <c r="AT191" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         </is>
       </c>
       <c r="AT194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         </is>
       </c>
       <c r="AT195" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         </is>
       </c>
       <c r="AT202" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
@@ -41528,7 +41528,7 @@
         </is>
       </c>
       <c r="AT203" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         </is>
       </c>
       <c r="AT204" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         </is>
       </c>
       <c r="AT205" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
